--- a/paper/source_data/ed3b_source_data.xlsx
+++ b/paper/source_data/ed3b_source_data.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One sheet per panel with exactly the plotted values, intervals, floored counts and labels. Each row names the aggregate file it was read from and that file's SHA-256.</t>
+          <t>One sheet per panel with exactly the plotted values, intervals, floored counts and labels. Each row names the aggregate file it was read from and that file's SHA-256, with one further column pair for each further file a row was read from.</t>
         </is>
       </c>
     </row>
@@ -496,12 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>**Extended Data Fig. 4 | Equal tuning, readout sensitivity and where BRAN loses eye information.** Same 26 conditions, 1,928 AI-READI development participants and five folds as Fig. 3.
-**a**, All 25 arms of the tuned benchmark, each with its own penalty chosen by nested cross-validation, and BRAN's native heads (square). Left, tuned macro AUROC with the fixed C = 1 estimate (open diamond). Right, BRAN combined minus each arm, with ticks at prespecified (black) and all-arm (grey) one-sided Bonferroni bounds.
-**b**, Macro AUROC of BRAN combined and four foundation-model arms with clinical data under fixed, shared and per-arm tuned penalties, with tuned minus fixed AUROC and each prespecified bound.
-**c**, Eye-alone macro AUROC and the prespecified decision family, compression loss (BRAN retinal input minus state) and input deficits (foundation model minus input), with bounds over eight tests and a 0.010 margin (dashed).
-**d**, R8 retinal-route retrain minus R7 and its acceptance gates.
-Points, estimates. Bars, 95% participant bootstrap intervals (1,000 shared draws) unless stated. Adverse results. Tuned BRAN combined tied RETFound-Green, DINOv3 and Labrador with clinical data, raw clinical values plus age, raw clinical and retinal concatenation, every PCA-64 arm and its own clinical route, and its prespecified bound cleared zero only against VisionFM (**a**). VisionFM with clinical data chose the lowest C on the grid in 57 of 130 condition-fold cells, so its tuned AUROC may be underestimated. BRAN's advantage was smallest under per-arm tuning (**b**). BRAN lost eye information when compressing its retinal input (**c**). R8 lowered eye-alone AUROC by 0.0051 [0.0015, 0.0089], failed two gates and was not adopted, and a later R8 check stopped on a technical failure (**d**). A label-free BRAN comparison and the original RETFound arm are PLACEHOLDER.</t>
+          <t>**Extended Data Fig. 4 | Equal tuning, readout sensitivity and where BRAN loses eye information.** Participants, conditions and folds as in Fig. 3. **a**, All 25 tuned-benchmark arms (penalty by nested cross-validation) and native heads (square). Left, tuned macro AUROC with the fixed C = 1 estimate. Right, BRAN combined minus each arm, with prespecified and all-arm one-sided Bonferroni bounds. **b**, BRAN combined and four foundation-model arms with clinical data under fixed, shared and per-arm tuned penalties, with tuned minus fixed AUROC and prespecified bounds. **c**, Eye-alone macro AUROC and the prespecified family of compression loss (BRAN retinal input minus state) and input deficits (foundation model minus input), with bounds over eight tests and a 0.010 margin. **d**, R8 retinal-route retrain minus the reported R7 model and acceptance gates. Points, estimates. Bars, participant bootstrap 95% intervals (1,000 shared draws) unless stated. Adverse results. Tuned BRAN combined tied RETFound-Green, DINOv3 and Labrador with clinical data, raw clinical values plus age, raw clinical and retinal concatenation, every PCA-64 arm and its clinical route, and its prespecified bound cleared zero only against VisionFM (**a**). VisionFM with clinical data chose the lowest C in 57 of 130 condition-fold cells and may be underestimated. BRAN's advantage was smallest under per-arm tuning (**b**). BRAN's compression of retinal input lost eye information (**c**). R8 lowered eye-alone AUROC by 0.0051 [0.0015, 0.0089], failed two gates and was not adopted, and a later R8 check failed technically (**d**). A label-free BRAN comparison and the original RETFound arm are PLACEHOLDER.</t>
         </is>
       </c>
     </row>
